--- a/144/DQ Templates and Instructions/Topic 3 DQ 1/Topic 3 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 3 DQ 1/Topic 3 DQ 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 3 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="358" documentId="8_{C5702531-EDB5-4409-B5CA-675AC228E6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE2646AC-1569-4277-A41A-5BBD53B8F34D}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="8_{C5702531-EDB5-4409-B5CA-675AC228E6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37C3A3E-D2BC-4E5E-95F2-8C02AF2E9255}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4FCF7FA6-22BB-4545-AB27-D5B8AACA448D}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={0235BCF7-F423-410C-AD78-31A725BD486C}</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{0235BCF7-F423-410C-AD78-31A725BD486C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/c2207d8d80c643cf9517ca6e311b34ae?sid=4b417298-8b85-49a8-af86-79a75296277b</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="100">
   <si>
@@ -369,7 +387,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +507,20 @@
       <color theme="0" tint="-4.9989318521683403E-2"/>
       <name val="Baguet Script"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1436,6 +1468,46 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1463,6 +1535,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -1475,29 +1607,29 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1511,222 +1643,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1739,6 +1655,14 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -1750,6 +1674,253 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1784,153 +1955,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="39" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2473,7 +2505,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{A66A1B58-D2D2-42E5-B9FA-16DA6F3D4A50}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2771,6 +2805,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F2" dT="2026-07-16T19:39:03.35" personId="{A66A1B58-D2D2-42E5-B9FA-16DA6F3D4A50}" id="{0235BCF7-F423-410C-AD78-31A725BD486C}">
+    <text>https://www.loom.com/share/c2207d8d80c643cf9517ca6e311b34ae?sid=4b417298-8b85-49a8-af86-79a75296277b</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1386620940</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/c2207d8d80c643cf9517ca6e311b34ae?sid=4b417298-8b85-49a8-af86-79a75296277b"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B51BD4A-B200-47DD-841D-A7B7D30FD324}">
   <dimension ref="B1:I11"/>
@@ -2784,53 +2832,53 @@
       <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="81"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="74"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="84"/>
     </row>
     <row r="4" spans="2:9" ht="30">
       <c r="B4" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="74"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="84"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="22"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="74"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D6" s="75"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="77"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="87"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
@@ -2866,7 +2914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7870B2E2-92BC-47AC-B93B-26715350F717}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7870B2E2-92BC-47AC-B93B-26715350F717}">
   <dimension ref="B1:N40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2889,14 +2937,14 @@
       <c r="C2" s="68" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="D2" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="120" t="s">
+      <c r="E2" s="127"/>
+      <c r="F2" s="206" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="121"/>
+      <c r="G2" s="207"/>
       <c r="H2"/>
       <c r="I2"/>
     </row>
@@ -2917,18 +2965,18 @@
       <c r="I4"/>
     </row>
     <row r="5" spans="2:14" ht="16.5" thickTop="1">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="119"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="42"/>
       <c r="E5" s="43">
         <v>15</v>
       </c>
-      <c r="F5" s="104" t="s">
+      <c r="F5" s="134" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="105"/>
+      <c r="G5" s="135"/>
       <c r="H5" s="44"/>
       <c r="I5" s="39"/>
     </row>
@@ -2943,10 +2991,10 @@
       <c r="E6" s="45">
         <v>15</v>
       </c>
-      <c r="F6" s="106" t="s">
+      <c r="F6" s="136" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="107"/>
+      <c r="G6" s="137"/>
       <c r="H6" s="46"/>
       <c r="I6" s="40"/>
       <c r="J6" s="58"/>
@@ -2966,10 +3014,10 @@
       <c r="E7" s="47">
         <v>16</v>
       </c>
-      <c r="F7" s="108" t="s">
+      <c r="F7" s="138" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="109"/>
+      <c r="G7" s="139"/>
       <c r="H7" s="44"/>
       <c r="I7" s="39"/>
       <c r="J7" s="58"/>
@@ -2989,10 +3037,10 @@
       <c r="E8" s="48">
         <v>16</v>
       </c>
-      <c r="F8" s="110" t="s">
+      <c r="F8" s="140" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="111"/>
+      <c r="G8" s="141"/>
       <c r="H8" s="46"/>
       <c r="I8" s="40"/>
       <c r="J8" s="58"/>
@@ -3029,10 +3077,10 @@
       </c>
       <c r="D10" s="42"/>
       <c r="E10" s="42"/>
-      <c r="F10" s="136" t="s">
+      <c r="F10" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="137"/>
+      <c r="G10" s="92"/>
       <c r="H10" s="49"/>
       <c r="I10" s="57"/>
       <c r="J10" s="58"/>
@@ -3046,8 +3094,8 @@
       <c r="C11" s="50"/>
       <c r="D11" s="50"/>
       <c r="E11" s="50"/>
-      <c r="F11" s="138"/>
-      <c r="G11" s="139"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="94"/>
       <c r="H11" s="49"/>
       <c r="I11" s="57"/>
       <c r="J11" s="58"/>
@@ -3058,13 +3106,13 @@
     </row>
     <row r="12" spans="2:14" ht="14.45" customHeight="1" thickBot="1">
       <c r="B12" s="50"/>
-      <c r="C12" s="112" t="s">
+      <c r="C12" s="142" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="113"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="141"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="96"/>
       <c r="H12" s="51"/>
       <c r="I12" s="58"/>
       <c r="J12" s="58"/>
@@ -3075,14 +3123,14 @@
     </row>
     <row r="13" spans="2:14" ht="15.75" thickBot="1">
       <c r="B13" s="50"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="117"/>
-      <c r="F13" s="131" t="s">
+      <c r="C13" s="145"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="147"/>
+      <c r="F13" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="131"/>
-      <c r="H13" s="132"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="152"/>
       <c r="I13" s="58"/>
       <c r="J13" s="59"/>
       <c r="K13" s="58"/>
@@ -3091,15 +3139,15 @@
       <c r="N13" s="58"/>
     </row>
     <row r="14" spans="2:14" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="135"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="153"/>
+      <c r="G14" s="154"/>
+      <c r="H14" s="155"/>
       <c r="I14" s="58"/>
       <c r="J14" s="58"/>
       <c r="K14" s="58"/>
@@ -3108,20 +3156,20 @@
       <c r="N14" s="58"/>
     </row>
     <row r="15" spans="2:14">
-      <c r="B15" s="125"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="100" t="s">
+      <c r="B15" s="99"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="102" t="s">
+      <c r="G15" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="98" t="s">
+      <c r="H15" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="145"/>
+      <c r="I15" s="115"/>
       <c r="J15" s="58"/>
       <c r="K15" s="58"/>
       <c r="L15" s="58"/>
@@ -3129,14 +3177,14 @@
       <c r="N15" s="58"/>
     </row>
     <row r="16" spans="2:14" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B16" s="128"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="145"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="102"/>
+      <c r="D16" s="102"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="133"/>
+      <c r="H16" s="129"/>
+      <c r="I16" s="115"/>
       <c r="J16" s="58"/>
       <c r="K16" s="58"/>
       <c r="L16" s="58"/>
@@ -3144,15 +3192,15 @@
       <c r="N16" s="58"/>
     </row>
     <row r="17" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B17" s="122" t="str">
+      <c r="B17" s="97" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with simple interest. Compute the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C17" s="123"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="84" t="s">
+      <c r="C17" s="98"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="123" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="52" t="s">
@@ -3168,14 +3216,14 @@
       <c r="N17" s="58"/>
     </row>
     <row r="18" spans="2:14" ht="35.25" customHeight="1" thickBot="1">
-      <c r="B18" s="128"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="90"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="102"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="121"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="109"/>
       <c r="J18" s="66"/>
       <c r="K18" s="58"/>
       <c r="L18" s="58"/>
@@ -3183,7 +3231,7 @@
       <c r="N18" s="58"/>
     </row>
     <row r="19" spans="2:14" ht="18" customHeight="1">
-      <c r="B19" s="198" t="s">
+      <c r="B19" s="69" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="65" t="s">
@@ -3195,10 +3243,10 @@
       <c r="E19" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="149"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="91"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="110"/>
       <c r="J19" s="66"/>
       <c r="K19" s="58"/>
       <c r="L19" s="58"/>
@@ -3206,14 +3254,14 @@
       <c r="N19" s="58"/>
     </row>
     <row r="20" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B20" s="201"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="92"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="114"/>
+      <c r="I20" s="111"/>
       <c r="J20" s="66"/>
       <c r="K20" s="58"/>
       <c r="L20" s="58"/>
@@ -3221,15 +3269,15 @@
       <c r="N20" s="58"/>
     </row>
     <row r="21" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B21" s="122" t="str">
+      <c r="B21" s="97" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with compounded monthly. Compute the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="84" t="s">
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="156"/>
+      <c r="G21" s="123" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="53" t="s">
@@ -3245,14 +3293,14 @@
       <c r="N21" s="58"/>
     </row>
     <row r="22" spans="2:14" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B22" s="128"/>
-      <c r="C22" s="129"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="87"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="102"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="157"/>
+      <c r="G22" s="124"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="112"/>
       <c r="J22" s="60"/>
       <c r="K22" s="61"/>
       <c r="L22" s="58"/>
@@ -3260,7 +3308,7 @@
       <c r="N22" s="58"/>
     </row>
     <row r="23" spans="2:14" ht="18" customHeight="1">
-      <c r="B23" s="198" t="s">
+      <c r="B23" s="69" t="s">
         <v>30</v>
       </c>
       <c r="C23" s="65" t="s">
@@ -3272,10 +3320,10 @@
       <c r="E23" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="82"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="88"/>
+      <c r="F23" s="157"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="113"/>
       <c r="J23" s="60"/>
       <c r="K23" s="61"/>
       <c r="L23" s="58"/>
@@ -3283,14 +3331,14 @@
       <c r="N23" s="58"/>
     </row>
     <row r="24" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B24" s="201"/>
-      <c r="C24" s="202"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="89"/>
+      <c r="B24" s="72"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="158"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="114"/>
       <c r="J24" s="60"/>
       <c r="K24" s="61"/>
       <c r="L24" s="58"/>
@@ -3298,15 +3346,15 @@
       <c r="N24" s="58"/>
     </row>
     <row r="25" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B25" s="122" t="str">
+      <c r="B25" s="97" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you put  $"&amp;Random!I19&amp;" monthly for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="142" t="s">
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="106" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="55" t="s">
@@ -3324,37 +3372,37 @@
       <c r="N25" s="58"/>
     </row>
     <row r="26" spans="2:14" ht="18" customHeight="1">
-      <c r="B26" s="125"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="126"/>
-      <c r="E26" s="126"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="93"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="100"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
+      <c r="F26" s="104"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="109"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="88"/>
       <c r="K26" s="61"/>
       <c r="L26" s="58"/>
       <c r="M26" s="58"/>
       <c r="N26" s="58"/>
     </row>
     <row r="27" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B27" s="128"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="143"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="94"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="102"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="113"/>
+      <c r="J27" s="89"/>
       <c r="K27" s="61"/>
       <c r="L27" s="58"/>
       <c r="M27" s="58"/>
       <c r="N27" s="58"/>
     </row>
     <row r="28" spans="2:14" ht="18" customHeight="1">
-      <c r="B28" s="198" t="s">
+      <c r="B28" s="69" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="65" t="s">
@@ -3363,44 +3411,44 @@
       <c r="D28" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="199" t="s">
+      <c r="E28" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="79"/>
-      <c r="G28" s="143"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="94"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="89"/>
       <c r="K28" s="58"/>
       <c r="L28" s="58"/>
       <c r="M28" s="58"/>
       <c r="N28" s="58"/>
     </row>
     <row r="29" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B29" s="201"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="80"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="95"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="111"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="90"/>
       <c r="K29" s="58"/>
       <c r="L29" s="58"/>
       <c r="M29" s="58"/>
       <c r="N29" s="58"/>
     </row>
     <row r="30" spans="2:14" ht="29.1" customHeight="1" thickBot="1">
-      <c r="B30" s="122" t="str">
+      <c r="B30" s="97" t="str">
         <f>IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payment (P) required to reach a future amount (FV) of $"&amp;Solutions!J22&amp;".00 after "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>Enter your name in C2 and your very own problem will appear here:)</v>
       </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="142" t="s">
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="103"/>
+      <c r="G30" s="106" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="55" t="s">
@@ -3418,37 +3466,37 @@
       <c r="N30" s="58"/>
     </row>
     <row r="31" spans="2:14" ht="18" customHeight="1">
-      <c r="B31" s="125"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="126"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="143"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="93"/>
+      <c r="B31" s="99"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="112"/>
+      <c r="J31" s="88"/>
       <c r="K31" s="58"/>
       <c r="L31" s="58"/>
       <c r="M31" s="58"/>
       <c r="N31" s="58"/>
     </row>
     <row r="32" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B32" s="128"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="94"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="102"/>
+      <c r="E32" s="102"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="107"/>
+      <c r="H32" s="110"/>
+      <c r="I32" s="113"/>
+      <c r="J32" s="89"/>
       <c r="K32" s="58"/>
       <c r="L32" s="58"/>
       <c r="M32" s="58"/>
       <c r="N32" s="58"/>
     </row>
     <row r="33" spans="2:14" ht="18" customHeight="1">
-      <c r="B33" s="198" t="s">
+      <c r="B33" s="69" t="s">
         <v>93</v>
       </c>
       <c r="C33" s="65" t="s">
@@ -3457,29 +3505,29 @@
       <c r="D33" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="200" t="s">
+      <c r="E33" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="79"/>
-      <c r="G33" s="143"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="94"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="113"/>
+      <c r="J33" s="89"/>
       <c r="K33" s="58"/>
       <c r="L33" s="58"/>
       <c r="M33" s="58"/>
       <c r="N33" s="58"/>
     </row>
     <row r="34" spans="2:14" ht="18" customHeight="1" thickBot="1">
-      <c r="B34" s="204"/>
-      <c r="C34" s="205"/>
-      <c r="D34" s="206"/>
-      <c r="E34" s="207"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="144"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="95"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="78"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="90"/>
       <c r="K34" s="58"/>
       <c r="L34" s="58"/>
       <c r="M34" s="58"/>
@@ -3576,8 +3624,29 @@
       <c r="N40" s="58"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Uko9MDTZ6zElRjgVp52FAUKaHa34+EpmTB0+IHEnLY08sb8ARx0F6hNVXBKzWOvy4mPfQjfDg55zQ1Bp99MQxQ==" saltValue="ARU2gN/FKjcpjaOrmy9l8A==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HBUmoshzQfujUApxiZOkmxr64phh4MabnD8OKjUO3K98CxY+zIl71v3ZiTGeuhMvZHrOlYhT2/GiSVuW0qoHaw==" saltValue="wNldlurn4DywqFAzkh+ebQ==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="37">
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J26:J29"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="C12:E13"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B14:E16"/>
+    <mergeCell ref="F13:H14"/>
     <mergeCell ref="J31:J34"/>
     <mergeCell ref="F10:G12"/>
     <mergeCell ref="B30:E32"/>
@@ -3594,27 +3663,6 @@
     <mergeCell ref="I26:I29"/>
     <mergeCell ref="F17:F20"/>
     <mergeCell ref="G17:G20"/>
-    <mergeCell ref="J26:J29"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="C12:E13"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B14:E16"/>
-    <mergeCell ref="F13:H14"/>
-    <mergeCell ref="F25:F29"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:I20 H22:I24 H26:J29">
     <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
@@ -3632,6 +3680,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5709,10 +5758,10 @@
       <c r="C2" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="151" t="s">
+      <c r="D2" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="152"/>
+      <c r="E2" s="195"/>
       <c r="H2"/>
       <c r="I2"/>
     </row>
@@ -5733,10 +5782,10 @@
       <c r="I4"/>
     </row>
     <row r="5" spans="2:9" ht="17.25" thickTop="1" thickBot="1">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="119"/>
+      <c r="C5" s="149"/>
       <c r="D5"/>
       <c r="E5"/>
       <c r="H5"/>
@@ -5750,11 +5799,11 @@
         <v>10</v>
       </c>
       <c r="D6"/>
-      <c r="E6" s="153" t="s">
+      <c r="E6" s="196" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="154"/>
-      <c r="G6" s="155"/>
+      <c r="F6" s="197"/>
+      <c r="G6" s="198"/>
       <c r="H6"/>
       <c r="I6"/>
     </row>
@@ -5766,11 +5815,11 @@
         <v>13</v>
       </c>
       <c r="D7"/>
-      <c r="E7" s="156" t="s">
+      <c r="E7" s="199" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="157"/>
-      <c r="G7" s="158"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="201"/>
       <c r="H7"/>
       <c r="I7"/>
     </row>
@@ -5795,10 +5844,10 @@
       </c>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" s="168" t="s">
+      <c r="F9" s="182" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="168"/>
+      <c r="G9" s="182"/>
       <c r="H9"/>
       <c r="I9"/>
     </row>
@@ -5821,61 +5870,61 @@
       <c r="I12"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" thickBot="1">
-      <c r="F13" s="169" t="s">
+      <c r="F13" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="170"/>
-      <c r="H13" s="170"/>
+      <c r="G13" s="184"/>
+      <c r="H13" s="184"/>
       <c r="I13"/>
     </row>
     <row r="14" spans="2:9" ht="16.899999999999999" customHeight="1" thickBot="1">
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="172"/>
-      <c r="H14" s="172"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="185"/>
+      <c r="G14" s="186"/>
+      <c r="H14" s="186"/>
       <c r="I14"/>
     </row>
     <row r="15" spans="2:9">
-      <c r="B15" s="72"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="173" t="s">
+      <c r="B15" s="82"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="175" t="s">
+      <c r="G15" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="159" t="s">
+      <c r="H15" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="161"/>
+      <c r="I15" s="204"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B16" s="75"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="76"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="174"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="160"/>
-      <c r="I16" s="161"/>
-    </row>
-    <row r="17" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B17" s="69" t="str">
+      <c r="B16" s="85"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="188"/>
+      <c r="G16" s="190"/>
+      <c r="H16" s="203"/>
+      <c r="I16" s="204"/>
+    </row>
+    <row r="17" spans="2:11" ht="30.75" thickBot="1">
+      <c r="B17" s="79" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with simple interest. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you make a one time deposite of  $5225 and leave the money for 8 years at an APR of 5.13% with simple interest. Compute the interest earned.</v>
       </c>
-      <c r="C17" s="70"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="180" t="s">
+      <c r="C17" s="80"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="179" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="33" t="s">
@@ -5886,17 +5935,17 @@
       </c>
     </row>
     <row r="18" spans="2:11" ht="34.9" customHeight="1" thickBot="1">
-      <c r="B18" s="75"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="76"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="178"/>
-      <c r="G18" s="181"/>
-      <c r="H18" s="162">
+      <c r="B18" s="85"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="192"/>
+      <c r="G18" s="180"/>
+      <c r="H18" s="171">
         <f>Financial!B20*(1+Financial!C20*Financial!E20)</f>
         <v>0</v>
       </c>
-      <c r="I18" s="165">
+      <c r="I18" s="168">
         <f>H18-Financial!B20</f>
         <v>0</v>
       </c>
@@ -5914,10 +5963,10 @@
       <c r="E19" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="178"/>
-      <c r="G19" s="181"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="166"/>
+      <c r="F19" s="192"/>
+      <c r="G19" s="180"/>
+      <c r="H19" s="172"/>
+      <c r="I19" s="169"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" thickBot="1">
       <c r="B20" s="25">
@@ -5935,21 +5984,21 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F20" s="179"/>
-      <c r="G20" s="182"/>
-      <c r="H20" s="164"/>
-      <c r="I20" s="167"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="170"/>
     </row>
     <row r="21" spans="2:11" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B21" s="69" t="str">
+      <c r="B21" s="79" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you make a one time deposite of  $"&amp;Random!J19&amp;" and leave the money for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% with compounded monthly. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you make a one time deposite of  $5225 and leave the money for 8 years at an APR of 5.13% with compounded monthly. Compute the interest earned.</v>
       </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="183"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="180" t="s">
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="174"/>
+      <c r="F21" s="176"/>
+      <c r="G21" s="179" t="s">
         <v>34</v>
       </c>
       <c r="H21" s="34" t="s">
@@ -5962,17 +6011,17 @@
       <c r="K21" s="15"/>
     </row>
     <row r="22" spans="2:11" ht="35.450000000000003" customHeight="1" thickBot="1">
-      <c r="B22" s="75"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="186"/>
-      <c r="G22" s="181"/>
-      <c r="H22" s="165" t="e">
+      <c r="B22" s="85"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="86"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="180"/>
+      <c r="H22" s="168" t="e">
         <f>Financial!B24*(1+Financial!C24/Financial!D24)^(Financial!D24*Financial!E24)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I22" s="162" t="e">
+      <c r="I22" s="171" t="e">
         <f>H22-Financial!B24</f>
         <v>#DIV/0!</v>
       </c>
@@ -5995,10 +6044,10 @@
       <c r="E23" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="186"/>
-      <c r="G23" s="181"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="163"/>
+      <c r="F23" s="177"/>
+      <c r="G23" s="180"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="172"/>
       <c r="J23" s="18"/>
       <c r="K23" s="15"/>
     </row>
@@ -6018,23 +6067,23 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F24" s="187"/>
-      <c r="G24" s="182"/>
-      <c r="H24" s="167"/>
-      <c r="I24" s="164"/>
+      <c r="F24" s="178"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="170"/>
+      <c r="I24" s="173"/>
       <c r="J24" s="18"/>
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="14.45" customHeight="1" thickBot="1">
-      <c r="B25" s="69" t="str">
+      <c r="B25" s="79" t="str">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the final value of an account into which you put  $"&amp;Random!I19&amp;" monthly for "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the interest earned.")</f>
         <v>Compute the final value of an account into which you put  $54.43 monthly for 8 years at an APR of 5.13% compounded monthly. Compute the interest earned.</v>
       </c>
-      <c r="C25" s="70"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="191"/>
-      <c r="G25" s="194" t="s">
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="165" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="35" t="s">
@@ -6049,36 +6098,36 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="72"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="192"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="165" t="e">
+      <c r="B26" s="82"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="163"/>
+      <c r="G26" s="166"/>
+      <c r="H26" s="168" t="e">
         <f>Financial!B29*((1+Financial!C29/Financial!D29)^(Financial!D29*Financial!E29)-1)/(Financial!C29/Financial!D29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I26" s="162">
+      <c r="I26" s="171">
         <f>Financial!B29*Financial!D29*Financial!E29</f>
         <v>0</v>
       </c>
-      <c r="J26" s="188" t="e">
+      <c r="J26" s="159" t="e">
         <f>H26-I26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="19.149999999999999" customHeight="1" thickBot="1">
-      <c r="B27" s="75"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="192"/>
-      <c r="G27" s="195"/>
-      <c r="H27" s="166"/>
-      <c r="I27" s="163"/>
-      <c r="J27" s="189"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="163"/>
+      <c r="G27" s="166"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="160"/>
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11">
@@ -6094,11 +6143,11 @@
       <c r="E28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="192"/>
-      <c r="G28" s="195"/>
-      <c r="H28" s="166"/>
-      <c r="I28" s="163"/>
-      <c r="J28" s="189"/>
+      <c r="F28" s="163"/>
+      <c r="G28" s="166"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="160"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" thickBot="1">
       <c r="B29" s="29">
@@ -6116,22 +6165,22 @@
         <f ca="1">Random!J20</f>
         <v>8</v>
       </c>
-      <c r="F29" s="193"/>
-      <c r="G29" s="196"/>
-      <c r="H29" s="167"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="190"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="167"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="173"/>
+      <c r="J29" s="161"/>
     </row>
     <row r="30" spans="2:11" ht="30.75" thickBot="1">
-      <c r="B30" s="69" t="e">
+      <c r="B30" s="79" t="e">
         <f ca="1">IF(C2="Your Name Here!", "Enter your name in C2 and your very own problem will appear here:)","Compute the monthly payment (P) required to reach a future amount (FV) of $"&amp;ROUND(Solutions!H22,2)&amp;" after "&amp;Random!J20&amp;" years at an APR of "&amp;Random!J21&amp;"% compounded monthly. Compute the total invested and the interest earned.")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="191"/>
-      <c r="G30" s="194" t="s">
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="165" t="s">
         <v>95</v>
       </c>
       <c r="H30" s="35" t="s">
@@ -6145,35 +6194,35 @@
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="72"/>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="192"/>
-      <c r="G31" s="195"/>
-      <c r="H31" s="165" t="e">
+      <c r="B31" s="82"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="163"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="168" t="e">
         <f>Financial!B34*(Financial!C34/Financial!D34)/((1+Financial!C34/Financial!D34)^(Financial!D34*Financial!E34)-1)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I31" s="162" t="e">
+      <c r="I31" s="171" t="e">
         <f>H31*Financial!D34*Financial!E34</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J31" s="188" t="e">
+      <c r="J31" s="159" t="e">
         <f>Financial!B34-Solutions!I31</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="75"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="192"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="166"/>
-      <c r="I32" s="163"/>
-      <c r="J32" s="189"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="163"/>
+      <c r="G32" s="166"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="172"/>
+      <c r="J32" s="160"/>
     </row>
     <row r="33" spans="2:10">
       <c r="B33" s="11" t="s">
@@ -6188,11 +6237,11 @@
       <c r="E33" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="192"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="166"/>
-      <c r="I33" s="163"/>
-      <c r="J33" s="189"/>
+      <c r="F33" s="163"/>
+      <c r="G33" s="166"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="172"/>
+      <c r="J33" s="160"/>
     </row>
     <row r="34" spans="2:10" ht="15.75" thickBot="1">
       <c r="B34" s="29">
@@ -6211,32 +6260,20 @@
         <f ca="1">E29</f>
         <v>8</v>
       </c>
-      <c r="F34" s="193"/>
-      <c r="G34" s="196"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="164"/>
-      <c r="J34" s="190"/>
+      <c r="F34" s="164"/>
+      <c r="G34" s="167"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="161"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="0drcGcBptdPjKYjxlrLCv8ldFhFAN9pxyHQIKqb75qpkjn1xDK2YCfnqzKn5wjYb+xD2XBby9mzwjXOH51eGTw==" saltValue="o5me4X/+omJPHU3V7qrs0g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="33">
-    <mergeCell ref="J31:J34"/>
-    <mergeCell ref="B30:E32"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="H31:H34"/>
-    <mergeCell ref="I31:I34"/>
-    <mergeCell ref="J26:J29"/>
-    <mergeCell ref="B25:E27"/>
-    <mergeCell ref="F25:F29"/>
-    <mergeCell ref="G25:G29"/>
-    <mergeCell ref="H26:H29"/>
-    <mergeCell ref="I26:I29"/>
-    <mergeCell ref="B21:E22"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
     <mergeCell ref="H18:H20"/>
     <mergeCell ref="I18:I20"/>
     <mergeCell ref="B5:C5"/>
@@ -6248,11 +6285,23 @@
     <mergeCell ref="B17:E18"/>
     <mergeCell ref="F17:F20"/>
     <mergeCell ref="G17:G20"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="B21:E22"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J26:J29"/>
+    <mergeCell ref="B25:E27"/>
+    <mergeCell ref="F25:F29"/>
+    <mergeCell ref="G25:G29"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="I26:I29"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="B30:E32"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="H31:H34"/>
+    <mergeCell ref="I31:I34"/>
   </mergeCells>
   <conditionalFormatting sqref="H18:I18">
     <cfRule type="expression" dxfId="6" priority="5">
@@ -6297,96 +6346,96 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:8">
-      <c r="B2" s="197" t="s">
+      <c r="B2" s="205" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="205"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="205"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
+      <c r="B3" s="205"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="205"/>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+      <c r="H3" s="205"/>
     </row>
     <row r="4" spans="2:8">
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="197"/>
+      <c r="B4" s="205"/>
+      <c r="C4" s="205"/>
+      <c r="D4" s="205"/>
+      <c r="E4" s="205"/>
+      <c r="F4" s="205"/>
+      <c r="G4" s="205"/>
+      <c r="H4" s="205"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="197"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
-      <c r="F5" s="197"/>
-      <c r="G5" s="197"/>
-      <c r="H5" s="197"/>
+      <c r="B5" s="205"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="205"/>
+      <c r="E5" s="205"/>
+      <c r="F5" s="205"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="205"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="197"/>
-      <c r="C6" s="197"/>
-      <c r="D6" s="197"/>
-      <c r="E6" s="197"/>
-      <c r="F6" s="197"/>
-      <c r="G6" s="197"/>
-      <c r="H6" s="197"/>
+      <c r="B6" s="205"/>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="205"/>
+      <c r="F6" s="205"/>
+      <c r="G6" s="205"/>
+      <c r="H6" s="205"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="197"/>
-      <c r="C7" s="197"/>
-      <c r="D7" s="197"/>
-      <c r="E7" s="197"/>
-      <c r="F7" s="197"/>
-      <c r="G7" s="197"/>
-      <c r="H7" s="197"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="205"/>
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="197"/>
-      <c r="E8" s="197"/>
-      <c r="F8" s="197"/>
-      <c r="G8" s="197"/>
-      <c r="H8" s="197"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+      <c r="G8" s="205"/>
+      <c r="H8" s="205"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="197"/>
-      <c r="E9" s="197"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="197"/>
-      <c r="H9" s="197"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
     </row>
     <row r="10" spans="2:8">
-      <c r="B10" s="197"/>
-      <c r="C10" s="197"/>
-      <c r="D10" s="197"/>
-      <c r="E10" s="197"/>
-      <c r="F10" s="197"/>
-      <c r="G10" s="197"/>
-      <c r="H10" s="197"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="205"/>
+      <c r="F10" s="205"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="205"/>
     </row>
     <row r="11" spans="2:8">
-      <c r="B11" s="197"/>
-      <c r="C11" s="197"/>
-      <c r="D11" s="197"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="197"/>
-      <c r="G11" s="197"/>
-      <c r="H11" s="197"/>
+      <c r="B11" s="205"/>
+      <c r="C11" s="205"/>
+      <c r="D11" s="205"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="205"/>
+      <c r="G11" s="205"/>
+      <c r="H11" s="205"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6397,25 +6446,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -6632,25 +6662,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B72C8343-FD67-49E2-BAD6-A975045FBBED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{318A24C3-90E3-418A-8A86-1647DBF244A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3428D67A-ACE8-4C76-8511-B437250C88C3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6667,4 +6698,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{318A24C3-90E3-418A-8A86-1647DBF244A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B72C8343-FD67-49E2-BAD6-A975045FBBED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>